--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
+        <v>98091</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566709.622714909</v>
+        <v>566710</v>
       </c>
       <c r="R2" t="n">
-        <v>6934728.201742919</v>
+        <v>6934728</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -767,19 +767,9 @@
           <t>2016-06-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-06-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98091</v>
+        <v>98103</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98103</v>
+        <v>98108</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98108</v>
+        <v>98117</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>504</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Guckusko</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98117</v>
+        <v>98130</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>504</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98130</v>
+        <v>98143</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98143</v>
+        <v>98146</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98146</v>
+        <v>98147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98147</v>
+        <v>98150</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 4922-2024 artfynd.xlsx
+++ b/artfynd/A 4922-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>109689056</v>
       </c>
       <c r="B2" t="n">
-        <v>98253</v>
+        <v>98261</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
